--- a/users_dup.xlsx
+++ b/users_dup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,425 +436,9690 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kbxwdh568</t>
+          <t>pllezj772</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fordziju@test.com</t>
+          <t>hpuhsmbu@test.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0847462505</t>
+          <t>0864641203</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>uiwvfk834</t>
+          <t>ddjusr438</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>juctdklg@test.com</t>
+          <t>qstezkhr@test.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0868803860</t>
+          <t>0845109959</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>izgyot795</t>
+          <t>jgtfez652</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jjtqtfsq@test.com</t>
+          <t>lbjicyvc@test.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0855614219</t>
+          <t>0854278427</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vstvki406</t>
+          <t>paqwji411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sdwgukhv@test.com</t>
+          <t>byaqftpz@test.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0813654359</t>
+          <t>0800335127</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xrzczd417</t>
+          <t>bofqkj723</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cstrxfwn@test.com</t>
+          <t>bnhyfpfd@test.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0853198277</t>
+          <t>0846773953</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vglush345</t>
+          <t>ohpfmy480</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>qlthfqjz@test.com</t>
+          <t>gonrqzuz@test.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0845447981</t>
+          <t>0801309131</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lqjmqe188</t>
+          <t>phuvur923</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dslwpeep@test.com</t>
+          <t>jvppsylb@test.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0893420268</t>
+          <t>0872591528</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rmkpoq831</t>
+          <t>nosogf410</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>azogtqvj@test.com</t>
+          <t>fiqphfgx@test.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0856670491</t>
+          <t>0857878491</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tbqnpl906</t>
+          <t>jvvmgw103</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>igptxmot@test.com</t>
+          <t>hnassyao@test.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0826550800</t>
+          <t>0899780803</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>abxcxs781</t>
+          <t>yhxiur956</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jvcmtawr@test.com</t>
+          <t>ompicqtf@test.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0840778558</t>
+          <t>0886468298</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wpbhcg107</t>
+          <t>ntekvy282</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fknosbyt@test.com</t>
+          <t>plvrguop@test.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0804968943</t>
+          <t>0802919755</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>buqvfm237</t>
+          <t>qsoyuy675</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lqzwwdzj@test.com</t>
+          <t>ismrjbno@test.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0862465904</t>
+          <t>0820522752</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wklxds452</t>
+          <t>lkjjsn970</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pvvqevjd@test.com</t>
+          <t>myjrszyd@test.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0845308922</t>
+          <t>0892256292</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jnlhzn177</t>
+          <t>fgueva256</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wjoxdhgw@test.com</t>
+          <t>byhkwugj@test.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0840999345</t>
+          <t>0809959821</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>zcaaxk299</t>
+          <t>ijpoeh769</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vyemtjkf@test.com</t>
+          <t>zcqyplaz@test.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0844869215</t>
+          <t>0811224517</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qsrzjm539</t>
+          <t>dikmze186</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hhvqbtmd@test.com</t>
+          <t>gcjfxxuu@test.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0895170094</t>
+          <t>0898614435</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eppbkx982</t>
+          <t>winypj116</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ouwxdpds@test.com</t>
+          <t>uzsuxowf@test.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0898080751</t>
+          <t>0869143091</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yllsoz123</t>
+          <t>raphfk289</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mqbcksdg@test.com</t>
+          <t>htqccrey@test.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0833911838</t>
+          <t>0857957608</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wjlosl785</t>
+          <t>kzfuxt281</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gaavhbfm@test.com</t>
+          <t>amqhltxp@test.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0883466057</t>
+          <t>0849183150</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wqsmom491</t>
+          <t>gzkcuo864</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ugwxdbee@test.com</t>
+          <t>kjeyrcfo@test.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0847810809</t>
+          <t>0849336916</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dup_1_buqvfm237</t>
+          <t>oyqire703</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lqzwwdzj@test.com</t>
+          <t>bmvgizak@test.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0801184622</t>
+          <t>0824262466</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dup_2_lqjmqe188</t>
+          <t>ldfzgo854</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dup_new_2@test.com</t>
+          <t>gfqturxs@test.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0893420268</t>
+          <t>0885563869</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dup_3_yllsoz123</t>
+          <t>qzlyxl806</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>mqbcksdg@test.com</t>
+          <t>wxbdwefp@test.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0833911838</t>
+          <t>0811437025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dup_4_rmkpoq831</t>
+          <t>fpkify865</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>azogtqvj@test.com</t>
+          <t>qjlcbtop@test.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0817129696</t>
+          <t>0896400983</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dup_5_vstvki406</t>
+          <t>akcdlu832</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>tgtjlvyd@test.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0832212469</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>safweg219</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>yxekmzts@test.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0810314952</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ypkwim601</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ickfazco@test.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0878854519</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>kwbzyl258</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fswwgbrh@test.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0867314092</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>nzqxna159</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>gzvpptaw@test.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0842195401</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>slymid168</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>zwbjhusd@test.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0856742030</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>qmyoog650</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>qmkjwegt@test.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0848007279</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ytdoyi219</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>zattrjoj@test.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0892637418</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>lkqyqu273</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rpmwctrs@test.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0837813971</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>oytkaa699</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>hxxqdelr@test.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0861698357</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ekdjvz124</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>adkcnwsq@test.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0833191658</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>gflphq910</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fmnhfwiy@test.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0815652479</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ebdrkf956</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ppdklzje@test.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0890468825</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>qbrhvt802</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>oufrdofg@test.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0813379117</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>vkqzbn700</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dhwvhllx@test.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0859288579</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>odpzlj435</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fzhlzwrb@test.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0867532329</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ttmrqk579</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>xyncuyvv@test.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0891630163</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>krerxn863</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>tkyaykma@test.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0844227679</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ebrmju305</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>gdabchti@test.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0867382861</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ttxury743</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ohvozwpe@test.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0831631339</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bvwbpc379</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>uluqitjf@test.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0824779626</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>udaxzi912</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pkuksvgv@test.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0867778798</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ggrhlg132</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>affzrjih@test.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0800946961</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>axlxxx897</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>gjzqjhrj@test.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0806885452</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ykthva576</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wioebuyj@test.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0864751308</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fqaeea720</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>slgolupt@test.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0840171411</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tkxffn633</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>swpsberc@test.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0842782680</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>skfrud876</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>qonormjv@test.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0888754054</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ivpjry668</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>vvicwpgi@test.com</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0805576654</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>zdacen678</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>yswlfvfb@test.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0822770961</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>wyebpt508</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>hopntoqh@test.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0852680740</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>rkucno829</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>vfwymvye@test.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0877876394</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>jwuime380</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>rmctonvb@test.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0812192590</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gsfelc207</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>fwonetzd@test.com</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0890416353</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>kuovtd261</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>dnvndxcw@test.com</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0827942084</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>jjsiaf869</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>qhjaeppi@test.com</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0839474923</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>vvxvqi384</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>yrkntgro@test.com</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0810851306</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>pbmgus734</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ibfdtvbz@test.com</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0895255441</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>nibinc633</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>tanqlpve@test.com</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0822729430</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ddzsbz580</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>gkzwchog@test.com</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0840543123</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>yjqpey613</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ovvdojtp@test.com</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0828504345</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>nmmcru447</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>hoklbppd@test.com</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0890950611</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>vthcfq798</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>oernggul@test.com</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0875603459</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bfcoax955</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>bbxroyjk@test.com</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0837687433</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cdyehm396</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>umieujqx@test.com</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0813951252</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>exbghr875</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>xuetlzfs@test.com</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0800143301</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>vprdfh240</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ewbmmnes@test.com</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0817306173</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>mopknw410</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>dskthmbo@test.com</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0812141849</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ahttos590</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>rqmwsbyy@test.com</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0839048052</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>mmpilc951</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>xkmohteo@test.com</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0871898722</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>iajnag891</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hrrfpetc@test.com</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0824844983</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fediwa520</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>mpzpkjzv@test.com</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0804790737</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fawhtn404</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>mwgatkgf@test.com</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0834541777</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>algjsj595</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>rmdrfenc@test.com</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0895717929</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>zydlfy421</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>nskhyoox@test.com</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0835788766</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cdeoqo973</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>tvrrqdie@test.com</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0874325874</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ynkbxf506</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>poqptghb@test.com</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0861585597</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>elbvvf668</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>uukhlwog@test.com</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0885165101</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>eqaacy634</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>pmfkimyh@test.com</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0868969441</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>utpzzt917</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>sdygqyrq@test.com</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0862047603</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>tunpsb580</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>sgfkpjdv@test.com</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0839541895</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>pjxzwi738</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>xuhnfbar@test.com</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0805104980</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>qwrzkx143</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>dgnbopfo@test.com</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0816758265</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>nfhael724</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ygmrztgc@test.com</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0800103067</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>mtfjkx462</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>zrxcwzqf@test.com</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0851006166</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fmrhhv237</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>kvvudzxy@test.com</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0853790471</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>xoxmne536</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>fyirrtre@test.com</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0856075819</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>bwlhol879</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>imbwcyeo@test.com</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0818433484</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tydtvq185</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>zplioqzi@test.com</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0872080836</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>pmrojv807</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ijwfikjl@test.com</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0817656512</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>atkhol389</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ycnjozpy@test.com</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0864443187</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cyehzd447</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>pklgihkr@test.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0806336701</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>pamlot513</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>xbmvoclg@test.com</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0855249649</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>hizhpe950</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>fwhohumm@test.com</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0835195675</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>diznge543</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>feiflyws@test.com</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0867490567</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>xmusdf442</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>rxlauyft@test.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0802150076</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>skhpsp181</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ndtvuxiz@test.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0810966148</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ermfyo660</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>orbmfbef@test.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0802590966</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>uxvgsx852</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>pktojauk@test.com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0852753918</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>fgjufj651</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>yivggcvg@test.com</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0855723296</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>nbqlqc950</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>vdqlvani@test.com</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0841872033</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>jvudtk957</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>oayomiqc@test.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0864090292</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>tblpeq616</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ywwbkzds@test.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0856447741</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>keindc919</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>pxvlhhvs@test.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0853847487</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ntcgkn998</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>xefkgoqp@test.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0876302970</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>mrfnfm915</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>rqagzbuc@test.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0887844419</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>csfedn120</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>kbvkbtgj@test.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0815517734</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ifzfdy561</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>tvghubzc@test.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0847115456</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>tjagdw954</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>aihosfet@test.com</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0877385203</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>jqskqv847</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>jrykbqro@test.com</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0806965690</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sibedm130</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>bfztfzxt@test.com</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0881237029</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>lpgzmz464</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ccjzhvdk@test.com</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0870231701</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>iozcwz589</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>xnrowodq@test.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0897455838</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>esgadj417</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>amudvinv@test.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0816144533</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>czwwhs270</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>weiuxsws@test.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0874475561</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>lrsdrd550</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>fuushyeu@test.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0847780251</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>hguaxx428</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>syrthhak@test.com</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0839518865</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>dmbgmc817</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>acyhqnjv@test.com</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0833020357</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>efoeif820</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>mevumkoy@test.com</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0890967944</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ediagk906</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>rakbxena@test.com</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0881569170</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>sruvnx284</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>vpilzzdq@test.com</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0824425463</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>oxpafi153</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>udfyznfn@test.com</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0873227812</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>scjpxe752</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>zriqfxvq@test.com</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0810341176</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>hsibzs638</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>zjjsvchj@test.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0809907552</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>vpwdpt799</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>wrddovrt@test.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0897100028</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ihwyak914</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>rgpdmbfq@test.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0897450667</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>utrcou521</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>lcsiudul@test.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0816857640</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>jsvsyk463</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ygkozycj@test.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0871814689</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>fxrvem999</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>lsmlbikq@test.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0888763827</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ukgxbr499</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ghxzajsb@test.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0816848860</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ldsqit752</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>zpgydkza@test.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0831723532</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>onehdv842</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>zqtqdaww@test.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0817013477</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>febzew913</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>urstaeqj@test.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0816715432</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cosetn626</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>xuegcdkd@test.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0845063192</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cyfgvz449</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>losscdzo@test.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0800003397</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>xcsnkd339</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>jxqrwlec@test.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0822106946</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>lwjupl252</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ipnqxjmz@test.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0848193585</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>tpwmjr708</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>zkrrnaxv@test.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0896482739</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>tpeods190</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>yrjhohdv@test.com</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0884986125</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>fscfhw971</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>flrkkwkt@test.com</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0897244892</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>hngmhd192</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>nqgtjkwg@test.com</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0842221724</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>nggwwp798</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ccgnmdqp@test.com</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0885679737</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>xmnujq273</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>bclnpltx@test.com</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0826446387</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>jazssf100</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>qphbdrot@test.com</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0818470029</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>lreiym608</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>mmiebevl@test.com</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0805007936</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>otsvet306</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>zxwmgchw@test.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0859957775</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>wzzfbx433</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>vrrhvltu@test.com</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0803903019</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>dsiixb994</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>xrrhsaoq@test.com</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0836374280</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>nuydzd833</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ibxhnxec@test.com</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0861070918</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>eixyrq194</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>rchwfwft@test.com</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0805712948</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>psgifm514</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ymjsupjd@test.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0806608089</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>dcdikh634</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>arklugpq@test.com</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0858557357</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>hnxzom200</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>emwnvlit@test.com</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>0868144160</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>bktofs570</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>rdeuptfo@test.com</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0816315442</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>gvvdpj259</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>luufbxcx@test.com</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0825982470</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>pvawwr111</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>zsrrxgoq@test.com</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0869921149</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>enrlbl345</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>yuljgkrd@test.com</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0856294317</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>zrrihj336</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ojifetba@test.com</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0862700655</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>jmeszf662</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>mlsrmjuv@test.com</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>0815201722</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>svtgkk265</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>fivjtrui@test.com</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>0893304793</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>myrbkv508</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>aqxfxxiv@test.com</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>0844551797</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>splhtd322</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>kgamgbow@test.com</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0804999618</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>enihpt862</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ozpqgket@test.com</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>0819070424</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>jieklj410</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>yolvtlyi@test.com</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>0824750462</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>kjeaaz410</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>qngcgfsq@test.com</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>0842520444</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>pwbdil814</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ybjmtnmr@test.com</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>0846368079</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>xobnok763</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>qdzumujn@test.com</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>0857000552</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>zfuesn203</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ehvfmehz@test.com</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>0899901234</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>hwmfpn656</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>pgkkrvgo@test.com</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0837430163</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>pmcrdd831</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>qfvasuks@test.com</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>0820620410</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ruysuw263</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>hgtekwjs@test.com</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>0806468713</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>dsynic302</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>lenmipzj@test.com</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>0808607353</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>hiecpg823</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>firealpg@test.com</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>0861153549</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ifvumg355</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>udaraauz@test.com</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>0858989322</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>eeweyr553</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>lqtdzuea@test.com</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>0815165407</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>hhzxqj823</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ywwzztdj@test.com</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>0879603123</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>mryrns183</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>gmjdznbn@test.com</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0842299189</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>yxohxj688</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ypsllzuf@test.com</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>0806762203</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>kjkugo229</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>fshoibpn@test.com</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>0873322322</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>yglcpw387</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>zwlddqzs@test.com</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>0881995763</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ovngdj462</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>fchtults@test.com</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0821359420</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>vuryns231</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>xnlqssus@test.com</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>0874140362</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>myfrro911</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ghfbxvqv@test.com</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>0833446671</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tbswlx358</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>aegbwoit@test.com</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>0809644184</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>dttbgb588</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>smajlmhw@test.com</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>0830702484</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>azzlei560</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>jrfckvix@test.com</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>0820093088</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>miiwcu542</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>iljfjxvf@test.com</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>0888325206</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tewkhy392</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>mdxyjrzi@test.com</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>0815224039</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>gecwgc553</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>dcggfggm@test.com</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>0838840700</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>gjgoxr665</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>sgxjjopf@test.com</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>0866691045</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>zbexxp483</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>fywkvgko@test.com</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>0852244837</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>zoixtr493</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>jaebihyf@test.com</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>0880886341</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>sslxds620</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>kufnqkkr@test.com</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>0881409519</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tbthco999</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>hobonobw@test.com</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>0833054128</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>bymqhp745</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>jigxkwuf@test.com</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>0837659617</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>bnowtq499</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>fltqrgxo@test.com</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>0897726791</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>wewwuw120</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>fvrgnkhp@test.com</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>0845114977</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>kxkbtk857</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>kixwibrt@test.com</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>0848480602</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>jihovh895</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ttjvbdbn@test.com</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>0877245759</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>zufjde108</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>xdbstnnk@test.com</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>0817357811</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>uipalq591</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>bebsglvb@test.com</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>0883131577</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>wdvbom754</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>geyhpfag@test.com</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>0846090684</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>whedbh812</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>afdfefiz@test.com</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>0836453230</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ariqas103</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>lvdsdccb@test.com</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>0878685257</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>bemilq580</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>depmrcwg@test.com</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>0884050765</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>dnmknr460</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>gzkuylzz@test.com</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>0841314195</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>uxmslc826</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ryhwwlko@test.com</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>0827943728</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>uteoyw125</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>sfnxeuje@test.com</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>0878399914</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>dsrazv289</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>glyenspo@test.com</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>0860007477</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>edfsja289</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>skdspfas@test.com</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>0804782789</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>miokfi891</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>wccesbdr@test.com</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>0817860639</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>vxtfku189</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>yxxgqvhs@test.com</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>0826522582</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>sdqwyt829</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>vlkwazcw@test.com</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>0826889215</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>pfnfkh748</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>eautylnq@test.com</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>0804773411</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ltuauo656</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ivkbwzrq@test.com</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>0817191444</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>kqjwfx933</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ggpebspm@test.com</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>0827142732</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ivzbql282</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>vzhgpwgr@test.com</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>0863807483</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ukqvkc422</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>xpsxpelk@test.com</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>0889386906</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>jifoft372</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>drzhuuer@test.com</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>0866075402</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>mkbyjt843</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ekbfzaud@test.com</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>0801917593</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>thqzjt603</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>cytauiqe@test.com</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>0896786389</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>tvheks381</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>eazecios@test.com</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>0833319649</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>qoiytj880</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>wdykeomf@test.com</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>0870364444</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>susnsd835</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>dwgiddmm@test.com</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>0887490709</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>uohtxl537</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>tkauydtw@test.com</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>0868660799</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ptfypc891</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>sxhxjtlp@test.com</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>0808058106</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>sdluci322</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>aotxyjjc@test.com</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>0888406882</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>vyjhvt929</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>rwxovjhg@test.com</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>0842215949</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ydzsdq595</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>qqxhnrwb@test.com</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>0873954543</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>tnfrvb821</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>dvcvhijg@test.com</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>0820730616</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>xmqecz658</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>kivmvpah@test.com</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>0867762915</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>lvkwtf499</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ktfhsakj@test.com</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>0844233935</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>elhqdl922</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>znzwpyjm@test.com</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>0822430456</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>vntxgw757</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>kugaxqyy@test.com</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>0853065038</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>fyfqny750</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>dmryatoa@test.com</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>0850246947</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>thjzal111</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>emwhgarf@test.com</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>0801860879</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>kxujiw943</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>cojvxavi@test.com</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>0877534693</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>eftnfx509</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>vuaoqgvc@test.com</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>0830892428</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>oldquq705</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>onjslgns@test.com</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>0837003845</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>eunbkq142</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>jjbpzvyl@test.com</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>0839652900</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>pqhnkj497</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>yulkafib@test.com</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>0852844339</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>vxshpr998</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ulqzeruz@test.com</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>0841031124</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ihorut270</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>vruiwmwn@test.com</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>0856453909</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>tmgkqh736</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>yrfsitwj@test.com</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>0886763038</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>xvthuv654</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>mzzwjekj@test.com</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>0843804252</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>vrkxmv358</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>lteppvnz@test.com</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>0884468170</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>mkxuqi344</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>bohjkiue@test.com</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>0843545499</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>yykrbx211</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>lurfbfgm@test.com</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>0835343938</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>lvqguq575</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>gdcamghf@test.com</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>0828994846</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>dovupu452</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>yiujjdjp@test.com</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>0890558403</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>nwbofa404</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>dtgvxqsw@test.com</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>0803234559</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ucrggi543</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>otsdhfzr@test.com</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>0809560959</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>vxvlhi402</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>sifezjyv@test.com</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>0894052057</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>fhfsjl875</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>kqyuohyv@test.com</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>0877600007</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ebuagb416</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>roaumnaw@test.com</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>0872342725</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>aubnly177</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>nhvzdfap@test.com</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>0853103142</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>amfrtn257</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>bakwqats@test.com</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>0814225874</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>nxbfwx764</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ouivgaxd@test.com</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>0886762747</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>rdpblp704</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>gpevpjtg@test.com</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>0864020559</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>gbydvi517</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>kbrmfdkf@test.com</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>0846229636</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>blgyao292</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>kdwmdvkq@test.com</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>0870995138</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>jawvec359</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>zcsulsla@test.com</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>0801340468</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>bcbrso135</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>oauvnhgh@test.com</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>0816515791</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>aoluer322</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>rjtahilp@test.com</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>0826384454</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>zcgfgx334</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>opcrlkbb@test.com</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>0847345791</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>jfdpns433</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>zftcomen@test.com</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>0868167867</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>czcshe648</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>sqaoeiww@test.com</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>0882752367</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>wwwoec983</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>biasmtnq@test.com</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>0811084842</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>pybhzf205</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>bbafjefa@test.com</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>0806728712</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>eglkht126</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>pfrlmrth@test.com</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>0882315421</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>yabfsk638</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>rujobbdb@test.com</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>0818373120</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>hqnxye325</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>baypdrcr@test.com</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>0829541504</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>yjjvxd398</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>cduvyyey@test.com</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>0878932585</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>vfzyhs902</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>vpbslfur@test.com</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>0868706732</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ijlmap804</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>djqeyczg@test.com</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>0847178776</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>memnnn393</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>seyjynfn@test.com</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>0828965403</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>agohbx390</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>kzcrwztp@test.com</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>0889840899</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>qzeuju247</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>ccdcamtu@test.com</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>0827051073</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>hwsrjd546</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>gbzrssht@test.com</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>0879486881</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>wvnuck858</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>oegvwsrr@test.com</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>0851921160</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>aktvzv271</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>lmbinfyx@test.com</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>0873594515</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ahomem984</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>rvulndza@test.com</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>0801226431</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>eaviwa940</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>cmsbpcnq@test.com</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>0868154261</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ikkmcg498</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>oojdemmw@test.com</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>0859381652</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>qahuss202</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>jnwfyutv@test.com</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>0867508081</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>mooqta123</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>jahbfftc@test.com</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>0853555767</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>kykaks269</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>gsumiaiw@test.com</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>0815432948</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>wxfocj684</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>qbawgofy@test.com</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>0885054479</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>bclwfn606</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>xncoxani@test.com</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>0863913169</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>athltm169</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>vieygqki@test.com</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>0852320086</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>eigopa657</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>nfturzhr@test.com</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>0894070447</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>unpkxg264</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>jynllblx@test.com</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>0883493851</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ytksjj153</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>losfdsva@test.com</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>0803598320</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ngdolu966</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ccrzzzij@test.com</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>0845980358</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>edpcfv752</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>wsrznoyt@test.com</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>0861128209</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>nmunri868</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>facnbqej@test.com</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>0878587282</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>mqpgiv246</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>uxbubjxb@test.com</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>0852780357</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>zypyyx148</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>pudatqns@test.com</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>0815304964</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>wofaky692</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ulzkzwhf@test.com</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>0861515427</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>nttsyk104</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>haqugnzx@test.com</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>0803672121</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>nadept850</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>rnocgjrf@test.com</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>0871440847</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>xnrcum253</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>bcqzkokf@test.com</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>0856228902</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ksqwij620</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>wsxevfbt@test.com</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>0811031983</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>nluffq540</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>pzjslrar@test.com</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>0862078118</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>owaegy714</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ixsmbfee@test.com</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>0890554522</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>aiglcz984</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ynhptlkb@test.com</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>0814917811</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>zkuhll841</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>oglbngdt@test.com</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>0810606406</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>srsbeu984</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>dgweturw@test.com</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>0828176282</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>vhldcm139</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>gtssmuuq@test.com</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>0855155980</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>iumaor601</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>dcddglon@test.com</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>0868869227</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>pglndh712</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>tmxebqmv@test.com</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>0880138360</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>qacigq214</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>nuaqbilx@test.com</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>0864816004</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>qomqwq558</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>csxufznk@test.com</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>0815702628</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>hyurly158</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>vrklqipd@test.com</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>0818078252</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>kutowr785</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>fkwaaami@test.com</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>0839025433</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>vyloeb348</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>dsgjwkph@test.com</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>0879443720</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>atwpee574</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>rlmrxqkh@test.com</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>0878235927</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>uwbfcv579</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>qgbvslce@test.com</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>0849485444</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>fsucuc319</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>tpmncmqz@test.com</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>0800223349</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>vqyeqd734</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>sblkqbyf@test.com</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>0812030533</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>dgldlk836</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>crvayffs@test.com</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0856464071</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>lgcgkt401</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>qptzqgfb@test.com</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>0805226073</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>xdkubu158</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>htogqlbe@test.com</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0857578592</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>rorvne147</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>lnklpyyl@test.com</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>0877613201</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>tgcybo997</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ucyfcbog@test.com</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0802668492</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>hklhtj810</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>rwipittr@test.com</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0862098088</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>tzfydi359</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ecfnzxvi@test.com</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0801584070</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>gqqisp487</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>zxsswweb@test.com</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>0887813152</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ppjbwd666</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>dvtkybri@test.com</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0817376657</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>dyjgrc604</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>hsdaobri@test.com</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0838511194</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>bxzpvb309</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ympfcrwd@test.com</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>0846267579</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>mydlpy886</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>jafcgjir@test.com</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>0887539994</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>jpdlpc574</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>jtvueuyx@test.com</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>0808205803</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>lspcvh562</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>huvfdhra@test.com</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>0859980184</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>xnyoso890</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>semmteve@test.com</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>0839566402</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>kttvix574</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>onhgfpts@test.com</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>0840118470</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>dtcsph801</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>lldhuljo@test.com</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>0880868924</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>ufxtor918</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>dyvgszll@test.com</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>0876630202</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>ambeyi667</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>qylpzrop@test.com</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>0854955195</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>gjhlcl962</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>qwmfmeea@test.com</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>0891345681</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>dlnbez521</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>itqvgvlt@test.com</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>0899134035</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ohwbrr309</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ilyswvmg@test.com</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>0863602316</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>lnrchx191</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>yleqimkc@test.com</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>0825214702</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>sezwfk520</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>qvbozxnv@test.com</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>0819000859</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>czkgxy888</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>wewqalfs@test.com</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>0883270174</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ruinmm314</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>culdvnnq@test.com</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>0883052524</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>qpzxdv287</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>zqnsggxa@test.com</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>0842997201</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>cofhmo631</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ftrgahys@test.com</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>0881029509</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ignrfq863</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>wjybttxk@test.com</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>0820379447</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>nskdab824</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>dwpdnnsm@test.com</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>0808710957</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ywcxxm961</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>vzctzgsl@test.com</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>0870385166</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>lugxyb452</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>kyjueskz@test.com</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>0884044298</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>mcsano666</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>qsrlkhpi@test.com</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>0838906698</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>yzimax771</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>qyrdpedg@test.com</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>0888503238</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>bhuupy853</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>qvjmrtyu@test.com</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>0871579437</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>idgaxf828</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>cucasfnl@test.com</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>0896791996</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>swvxno710</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>agnnyynh@test.com</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>0859376388</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>fkhdlr952</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>plbqsthy@test.com</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>0892227284</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>uhimtl459</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>rragpymt@test.com</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>0878235320</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>uhoahx602</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>btlgaurs@test.com</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>0851382675</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>cuehce563</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>vvjaurai@test.com</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>0853507111</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>ndirao927</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>vgisdzdf@test.com</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>0855640692</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>pvualk406</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>vybbsqyt@test.com</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>0859875961</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>edfkhl200</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>pxeuquvi@test.com</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>0886334976</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>rdsbtr597</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ocddzmhh@test.com</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>0898077092</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>xavotf662</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>lknzgfbk@test.com</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>0897816648</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>ppzzad683</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>cunvtwpr@test.com</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>0871236566</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>vamczr132</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>bihtbauk@test.com</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>0890968174</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>oibqdc893</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>fkhemank@test.com</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>0872240948</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>qclobd872</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>wairlaza@test.com</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>0884797747</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>pzphrt103</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>oqsszlos@test.com</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>0865086433</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>bfynaz855</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ewgpyoxi@test.com</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>0830324429</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>apcrfm690</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>rjxwuqyt@test.com</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>0813666997</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>vixrfh304</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>xqahrkvh@test.com</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>0866832866</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>xleafw775</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>rtquoxuw@test.com</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>0807520577</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>kvuknf653</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>soumobkt@test.com</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>0867671945</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>flohcx993</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>rwdbqonk@test.com</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>0825543759</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>jxojsi189</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>xzfytson@test.com</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>0877815609</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>aubyzv586</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ztuungnr@test.com</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>0826552284</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>orotgy639</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>wlbrtjgb@test.com</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>0881082936</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>oaajol425</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>attystof@test.com</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>0892963036</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>wopkib890</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>mesofuld@test.com</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>0844516636</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>czbhfr484</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>ctkozomz@test.com</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>0822504928</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>mvjsdc804</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>psocdooo@test.com</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>0845790858</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>fesmlb276</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>pcxbtjgk@test.com</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>0883410557</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>rxknty524</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ylvfkcvs@test.com</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>0852685904</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>leyvro459</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>pyufbgna@test.com</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>0864489515</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>yshtid736</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>oyfqpuvr@test.com</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>0871041842</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ikifkr133</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>wzuyhndq@test.com</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>0824001207</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>nldbhh452</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>xgwrajch@test.com</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>0866101680</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>zmknia261</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>aysruxgk@test.com</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>0873394674</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>uijgzn204</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>dzbjcqlh@test.com</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>0865677400</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>pfosvb293</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>vgdecrhw@test.com</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>0807016342</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>fdxwlp325</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>pfgmoeho@test.com</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>0895738507</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>kxsbte293</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>tqgoefbl@test.com</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>0884078122</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>zssgzj179</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>mhmvjjar@test.com</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>0815586587</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>gsgqqv285</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>nqzceenx@test.com</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>0863579207</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>fnfxgr660</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>nhripvoh@test.com</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>0806308098</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>azbruc211</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>xtkflxws@test.com</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>0834593936</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>ppsrpl966</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>btudpzgb@test.com</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>0816046237</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>rtisuo624</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ywryblni@test.com</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>0878811045</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ooxmsa567</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>dhhcoyzh@test.com</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>0849717372</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>zybmck825</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>nbbujxkq@test.com</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>0863882221</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>mqvcty161</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>zyrtpaco@test.com</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>0838537170</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>llzvmm443</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ynhblcla@test.com</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>0851016269</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>gaawox973</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>xklpcdas@test.com</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>0842956994</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>xlziat411</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>shkaifgo@test.com</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>0881860587</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>ftxsgm429</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>cbdsqqfs@test.com</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>0859456773</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>agcfbm615</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>myswoszt@test.com</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>0832946306</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>amjgao410</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>yqjccelu@test.com</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>0879310466</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>kwefsb500</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>elfeurbd@test.com</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>0802524244</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>atbjtv965</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>qvvhjzom@test.com</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>0893390123</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>jjupqd969</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>msmwrhhx@test.com</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>0870135176</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>yrqnnp718</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>xurwzaoa@test.com</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>0898317784</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>vwqyox715</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>datxsdhs@test.com</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>0875868513</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>cwqfzv596</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>adyclqck@test.com</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>0875250892</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>qfsyti341</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>rzxnuirk@test.com</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>0857491073</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>vdlhiq105</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>szdrjfbn@test.com</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>0896876469</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>ygwunk473</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>nwyiufmr@test.com</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>0882912035</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>aubdwq823</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>ndlexglz@test.com</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>0855661501</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>yxzjor792</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>clrqqfnv@test.com</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>0855316641</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>grgcew260</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>xuomdxla@test.com</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>0800346506</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>qysblh714</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>mguzlqtq@test.com</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>0822745262</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>uituux815</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>rvgwaqtw@test.com</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>0844526913</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>dzajdu246</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ypdhefoz@test.com</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>0847110939</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>adwedz758</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>gvcddksb@test.com</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>0855591781</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>cvwyzk515</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>hczkhygd@test.com</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>0824085609</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>heuvqd270</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ytlopdnn@test.com</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>0894709166</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>cshskg241</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>tavrspfp@test.com</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>0881612524</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>srozqr123</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>xgtgafpt@test.com</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>0839063579</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>tkigpb254</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>gnszekit@test.com</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>0815868615</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>ztbigl888</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>dqhkroqw@test.com</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>0863110445</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>arpuwa741</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>vgezsdtq@test.com</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>0871189901</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>guleiu112</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>fapfzvrv@test.com</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>0855301416</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>dokpim764</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>mwhxjyqs@test.com</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>0824872555</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>eohphu810</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>zqeauowf@test.com</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>0861225687</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>wsyqth984</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>sijvialq@test.com</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>0895821951</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>yjulwb385</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>xprshsey@test.com</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>0855784387</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>apffnw763</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>prvtjsrm@test.com</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>0893511072</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>vihyjb301</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>fotdqafd@test.com</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>0862401675</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>hvzlbl357</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>czyzjpcg@test.com</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>0897178542</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>hyrgtr797</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>ucgcbehu@test.com</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>0867271927</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>ekkwnm390</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>cwwnvflg@test.com</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>0853244406</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>bejxys502</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>ewdrwmhc@test.com</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>0847446543</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ataqbt680</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>hmotlphs@test.com</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>0835264674</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>echvzi843</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>pxdwhlmr@test.com</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>0803392484</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>tsdlbz127</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>sfgnnwsa@test.com</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>0881117716</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>dwcpix875</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>hgrvpzob@test.com</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>0890669951</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>nghsgu199</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>ekokufhw@test.com</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>0876349319</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>ooojka729</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>bouvdtnv@test.com</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>0814567506</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>rmeibl860</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>ighfdkrj@test.com</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>0840305794</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>wwpswx835</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>vyodbkio@test.com</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>0805342425</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>fzwygz111</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>xtqdeeio@test.com</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>0889937265</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>lbcfow254</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>qowehbcb@test.com</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>0843038741</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>zqtewp986</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>yfgvhwqp@test.com</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>0830240652</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>nlluie269</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>zmkuaglf@test.com</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>0818093131</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>xrbysu343</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>yefptbeb@test.com</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>0816534762</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>nwsjxg878</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>rirzbrgq@test.com</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>0884864106</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>eihfun298</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>rgcbgcbk@test.com</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>0876675134</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>tnfswx180</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>xpxsdnbq@test.com</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>0898031503</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>gwdskw261</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>pdlspgeo@test.com</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>0804664511</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>tiabye518</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>qrivolpd@test.com</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>0861533929</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>zwzpyj190</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>iieasuvu@test.com</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>0816725795</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>yftgsy740</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>qlzcjtog@test.com</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>0855156002</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>mshupo219</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>wonaftqr@test.com</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>0870861707</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>npphhu109</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>oiojqdts@test.com</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>0895848426</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>lhueke982</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>lpcvwtbb@test.com</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>0867960704</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>nrzwjc433</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>dynqlmjd@test.com</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>0850958809</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>sskanj967</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>epdmcstz@test.com</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>0887255923</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>hnovhr790</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>zbklrypd@test.com</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>0863073233</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>xlmuyq221</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>rorgbtnc@test.com</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>0838184005</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>pmfmek821</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>svfsznnz@test.com</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>0803003316</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ezzehd961</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>kxoxkopm@test.com</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>0841813221</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>hbjuag216</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>kteljudl@test.com</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>0870964107</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>kzmppp259</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>qrwxtjsl@test.com</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>0853537709</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>bdlqlh360</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>bpkbypcp@test.com</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>0840510504</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>oxoxgf484</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>rcmjjmlr@test.com</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>0830864624</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>iukefl537</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>deeoyzio@test.com</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>0880843250</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>hxhywy621</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>esvoosqj@test.com</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>0802668561</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>gilmgz793</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>amabgivn@test.com</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>0812106151</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>lqbnwu517</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>uahonkge@test.com</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>0859608751</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>ouidyt102</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>vvvujpsu@test.com</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>0828487732</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>rwvqxu505</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>jgeprtal@test.com</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>0821847808</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>rqhlwf994</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>tjmfcumv@test.com</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>0867273731</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>apupqj916</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>cxjauvtl@test.com</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>0827832530</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>noaxqv272</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>iesamhvf@test.com</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>0833351852</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ihemhz268</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>igfgytko@test.com</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>0845291622</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>jypwrx230</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>dnfukfsb@test.com</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>0895339495</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>paihmy660</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>lafsbfcx@test.com</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>0838108656</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>aeoqvc464</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>mpvyknip@test.com</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>0867869481</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>spmaru711</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>cweampjp@test.com</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>0857305778</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>hwvwfk434</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>otoaugje@test.com</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>0822117983</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>tjdwwx812</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>eblacphg@test.com</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>0814896528</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>wyhnuq481</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>cdxqjrsa@test.com</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>0846594822</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>joaqeh731</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>uwvdguhc@test.com</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>0835210115</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>stnqzn410</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>gycxatay@test.com</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>0845859548</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>dup_1_dokpim764</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>mwhxjyqs@test.com</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>0813455264</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>dup_2_mkxuqi344</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>dup_new_2@test.com</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>0843545499</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>dup_3_hyrgtr797</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ucgcbehu@test.com</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>0867271927</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>dup_4_ggrhlg132</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>affzrjih@test.com</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>0833267497</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>dup_5_zqtewp986</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
           <t>dup_new_5@test.com</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0813654359</t>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>0830240652</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>dup_6_dcdikh634</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>arklugpq@test.com</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>0858557357</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>dup_7_qclobd872</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>wairlaza@test.com</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>0863839066</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>dup_8_qacigq214</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>dup_new_8@test.com</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>0864816004</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>dup_9_zoixtr493</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>jaebihyf@test.com</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>0880886341</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>dup_10_dzajdu246</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ypdhefoz@test.com</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>0885429825</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>dup_11_vrkxmv358</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>dup_new_11@test.com</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>0884468170</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>dup_12_rorvne147</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>lnklpyyl@test.com</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>0877613201</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>dup_13_eunbkq142</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>jjbpzvyl@test.com</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>0845961826</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>dup_14_cdeoqo973</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>dup_new_14@test.com</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>0874325874</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>dup_15_lspcvh562</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>huvfdhra@test.com</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>0859980184</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>dup_16_lwjupl252</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>ipnqxjmz@test.com</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>0817613042</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>dup_17_fpkify865</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>dup_new_17@test.com</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>0896400983</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>dup_18_kykaks269</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>gsumiaiw@test.com</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>0815432948</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>dup_19_qmyoog650</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>qmkjwegt@test.com</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>0807296771</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>dup_20_gsgqqv285</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>dup_new_20@test.com</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>0863579207</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>dup_21_nmunri868</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>facnbqej@test.com</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>0878587282</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>dup_22_azbruc211</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>xtkflxws@test.com</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>0878638036</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>dup_23_udaxzi912</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>dup_new_23@test.com</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>0867778798</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>dup_24_idgaxf828</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>cucasfnl@test.com</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>0896791996</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>dup_25_whedbh812</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>afdfefiz@test.com</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>0839507311</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>dup_26_pbmgus734</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>dup_new_26@test.com</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>0895255441</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>dup_27_dup_26_pbmgus734</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>dup_new_26@test.com</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>0895255441</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>dup_28_jvudtk957</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>oayomiqc@test.com</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>0885414713</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>dup_29_qahuss202</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>dup_new_29@test.com</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>0867508081</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>dup_30_vvxvqi384</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>yrkntgro@test.com</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>0810851306</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>dup_31_kjeaaz410</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>qngcgfsq@test.com</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>0851600292</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>dup_32_lbcfow254</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>dup_new_32@test.com</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>0843038741</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>dup_33_atkhol389</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>ycnjozpy@test.com</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>0864443187</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>dup_34_ooojka729</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>bouvdtnv@test.com</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>0839582796</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>dup_35_tvheks381</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>dup_new_35@test.com</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>0833319649</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>dup_36_ihorut270</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>vruiwmwn@test.com</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>0856453909</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>dup_37_sibedm130</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>bfztfzxt@test.com</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>0855825306</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>dup_38_tsdlbz127</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>dup_new_38@test.com</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>0881117716</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>dup_39_zmknia261</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>aysruxgk@test.com</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>0873394674</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>dup_40_lqbnwu517</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>uahonkge@test.com</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>0864859037</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>fail_email_1_exva</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>0835369287</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>fail_phone_2_ahwr</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>johqjiwj@test.com</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>fail_both_3_vzhm</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>fail_email_4_yvqy</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>invalid_email</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>0811942467</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>fail_phone_5_jeof</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>rvmkdcpq@test.com</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>fail_both_6_hkwh</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>test@test</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>08123456789</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>fail_email_7_yxur</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>0869785663</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>fail_phone_8_wqiz</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>xkvcerhm@test.com</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>fail_both_9_rwso</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>fail_email_10_bexf</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>0862208095</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>fail_phone_11_xate</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>gwothiap@test.com</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>abcdefghij</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>fail_both_12_abxs</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>test@</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>fail_email_13_wytj</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>test@.com</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>0821945081</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>fail_phone_14_avfo</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>echbljps@test.com</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>fail_both_15_lown</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>invalid_email</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>abcdefghij</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>fail_email_16_pipz</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>0830601009</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>fail_phone_17_mrni</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>ukomupdp@test.com</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>abcdefghij</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>fail_both_18_nrae</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>abcdefghij</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>fail_email_19_xpal</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>@test.com</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>0849407281</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>fail_phone_20_zptn</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>vpazxrsm@test.com</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>fail_both_21_crvy</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>test@</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>081234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>fail_email_22_mzct</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>test@test.c</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>0820012214</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>fail_phone_23_euyq</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>kvgvjfmx@test.com</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>fail_both_24_xrux</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>test@.com</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>fail_email_25_mpzf</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>test@test</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>0874608039</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>fail_phone_26_ggml</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>hexirxbf@test.com</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>abcdefghij</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>fail_both_27_rtns</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>test@</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>fail_email_28_mmzh</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>test@test</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>0880776333</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>fail_phone_29_dgwi</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>seuzzdkl@test.com</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>081234567a</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>fail_both_30_gyoz</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>test@.com</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>abcdefghij</t>
         </is>
       </c>
     </row>
